--- a/data/processed/positivacao/2023-06_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-06_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25491,7 +25491,7 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B968" t="inlineStr"/>
@@ -36999,7 +36999,7 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr"/>
@@ -65683,7 +65683,7 @@
     <row r="2515">
       <c r="A2515" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2515" t="inlineStr"/>
@@ -67380,12 +67380,12 @@
       <c r="A2581" t="inlineStr"/>
       <c r="B2581" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 11 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 8.350,91
+          <t>Vendedor 1 - VENDEDOR 01: positivou 11 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 8.350,91
 Vendedor 18 - LOJA: positivou 119 cliente(s), não positivou 741 cliente(s) - Total vendido: R$ 55.842,43
-Vendedor 3 - FERNANDA: positivou 103 cliente(s), não positivou 339 cliente(s) - Total vendido: R$ 150.307,24
-Vendedor 4 - DANIELA: positivou 83 cliente(s), não positivou 574 cliente(s) - Total vendido: R$ 51.545,28
+Vendedor 3 - VENDEDOR 03: positivou 103 cliente(s), não positivou 339 cliente(s) - Total vendido: R$ 150.307,24
+Vendedor 4 - VENDEDOR 04: positivou 83 cliente(s), não positivou 574 cliente(s) - Total vendido: R$ 51.545,28
 Vendedor 5 - SITE: positivou 6 cliente(s), não positivou 439 cliente(s) - Total vendido: R$ 656,35
-Vendedor 8 - RAFAEL: positivou 2 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 748,60</t>
+Vendedor 8 - VENDEDOR 08: positivou 2 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 748,60</t>
         </is>
       </c>
       <c r="C2581" t="inlineStr"/>
